--- a/day02/T.V.xlsx
+++ b/day02/T.V.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python\python-course-assignments\python-course-assignments\day02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D067D0-5EEE-4DB2-9831-752CEC74204C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B58DB3-F42E-49CD-B0FD-A2733785DCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{60846883-93A2-42CD-91A5-DE46BEFCF260}"/>
   </bookViews>
